--- a/data/raw/GLNPO 2024 Spring/Erie/D100/ER 92 D100 Spring 2024 24GE03I93 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Erie/D100/ER 92 D100 Spring 2024 24GE03I93 Zoop.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\GLNPO 2024 Spring\Erie\D100\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Erie\D100\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3842CFED-C105-40B4-B56D-DA39C74D3D43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D52B578-E684-4FF0-BFE6-C731209F9AE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5A6E5FA3-7B75-4989-850D-07454B29D73D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5A6E5FA3-7B75-4989-850D-07454B29D73D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="22" r:id="rId2"/>
+    <pivotCache cacheId="6" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -6704,7 +6704,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F6441CF6-97DD-433D-854C-8E6F4EAECB29}" name="PivotTable3" cacheId="22" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F6441CF6-97DD-433D-854C-8E6F4EAECB29}" name="PivotTable3" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="T2:Y24" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="16">
     <pivotField showAll="0"/>
@@ -7177,24 +7177,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D166227-B8EA-4D18-B0B4-6BA6ABAE192C}">
   <dimension ref="A1:Y334"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="31.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="31.88671875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.88671875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="4" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="3" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="2.44140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7250,7 +7250,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -7309,7 +7309,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -7380,7 +7380,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -7445,7 +7445,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -7510,7 +7510,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -7578,7 +7578,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -7646,7 +7646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -7714,7 +7714,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -7779,7 +7779,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -7844,7 +7844,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -7912,7 +7912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -7980,7 +7980,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -8045,7 +8045,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -8110,7 +8110,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -8178,7 +8178,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -8249,7 +8249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -8317,7 +8317,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -8388,7 +8388,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -8456,7 +8456,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -8524,7 +8524,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -8592,7 +8592,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -8660,7 +8660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -8728,7 +8728,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -8799,7 +8799,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -8852,7 +8852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -8914,7 +8914,7 @@
         <v>0.995</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -8974,7 +8974,7 @@
         <v>1.0029999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -9036,7 +9036,7 @@
         <v>0.997</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -9096,7 +9096,7 @@
         <v>1.0009999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -9156,7 +9156,7 @@
       </c>
       <c r="V30" s="17"/>
     </row>
-    <row r="31" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -9216,7 +9216,7 @@
       </c>
       <c r="V31" s="17"/>
     </row>
-    <row r="32" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -9274,7 +9274,7 @@
       <c r="U32" s="16"/>
       <c r="V32" s="17"/>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -9327,7 +9327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -9380,7 +9380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -9433,7 +9433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>18</v>
       </c>
@@ -9486,7 +9486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -9539,7 +9539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -9592,7 +9592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -9645,7 +9645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>18</v>
       </c>
@@ -9698,7 +9698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -9751,7 +9751,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -9804,7 +9804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -9857,7 +9857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -9910,7 +9910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -9966,7 +9966,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -10019,7 +10019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -10072,7 +10072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -10128,7 +10128,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -10181,7 +10181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -10234,7 +10234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -10287,7 +10287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -10340,7 +10340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -10393,7 +10393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -10446,7 +10446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -10499,7 +10499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -10552,7 +10552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -10605,7 +10605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -10658,7 +10658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -10711,7 +10711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -10764,7 +10764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -10817,7 +10817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -10870,7 +10870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>18</v>
       </c>
@@ -10923,7 +10923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -10976,7 +10976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>18</v>
       </c>
@@ -11029,7 +11029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>18</v>
       </c>
@@ -11082,7 +11082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>18</v>
       </c>
@@ -11135,7 +11135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>18</v>
       </c>
@@ -11188,7 +11188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>18</v>
       </c>
@@ -11241,7 +11241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -11294,7 +11294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -11347,7 +11347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -11400,7 +11400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -11453,7 +11453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>18</v>
       </c>
@@ -11506,7 +11506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -11559,7 +11559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>18</v>
       </c>
@@ -11612,7 +11612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>18</v>
       </c>
@@ -11665,7 +11665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>18</v>
       </c>
@@ -11718,7 +11718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>18</v>
       </c>
@@ -11771,7 +11771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>18</v>
       </c>
@@ -11824,7 +11824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>18</v>
       </c>
@@ -11877,7 +11877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>18</v>
       </c>
@@ -11930,7 +11930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>18</v>
       </c>
@@ -11983,7 +11983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>18</v>
       </c>
@@ -12036,7 +12036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>18</v>
       </c>
@@ -12089,7 +12089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>18</v>
       </c>
@@ -12142,7 +12142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>18</v>
       </c>
@@ -12195,7 +12195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>18</v>
       </c>
@@ -12248,7 +12248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>18</v>
       </c>
@@ -12301,7 +12301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>18</v>
       </c>
@@ -12354,7 +12354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>18</v>
       </c>
@@ -12407,7 +12407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>18</v>
       </c>
@@ -12460,7 +12460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>18</v>
       </c>
@@ -12513,7 +12513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>18</v>
       </c>
@@ -12566,7 +12566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>18</v>
       </c>
@@ -12619,7 +12619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>18</v>
       </c>
@@ -12672,7 +12672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>18</v>
       </c>
@@ -12725,7 +12725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>18</v>
       </c>
@@ -12778,7 +12778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -12831,7 +12831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>18</v>
       </c>
@@ -12884,7 +12884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>18</v>
       </c>
@@ -12937,7 +12937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>18</v>
       </c>
@@ -12990,7 +12990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>18</v>
       </c>
@@ -13043,7 +13043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>18</v>
       </c>
@@ -13096,7 +13096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>18</v>
       </c>
@@ -13149,7 +13149,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>18</v>
       </c>
@@ -13202,7 +13202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>18</v>
       </c>
@@ -13255,7 +13255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>18</v>
       </c>
@@ -13308,7 +13308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>18</v>
       </c>
@@ -13361,7 +13361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>18</v>
       </c>
@@ -13414,7 +13414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>18</v>
       </c>
@@ -13467,7 +13467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>18</v>
       </c>
@@ -13520,7 +13520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>18</v>
       </c>
@@ -13573,7 +13573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>18</v>
       </c>
@@ -13626,7 +13626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>18</v>
       </c>
@@ -13679,7 +13679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>18</v>
       </c>
@@ -13732,7 +13732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>18</v>
       </c>
@@ -13785,7 +13785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>18</v>
       </c>
@@ -13838,7 +13838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>18</v>
       </c>
@@ -13894,7 +13894,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>18</v>
       </c>
@@ -13947,7 +13947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>18</v>
       </c>
@@ -14000,7 +14000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>18</v>
       </c>
@@ -14053,7 +14053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>18</v>
       </c>
@@ -14106,7 +14106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>18</v>
       </c>
@@ -14159,7 +14159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>18</v>
       </c>
@@ -14212,7 +14212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>18</v>
       </c>
@@ -14265,7 +14265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>18</v>
       </c>
@@ -14318,7 +14318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>18</v>
       </c>
@@ -14371,7 +14371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>18</v>
       </c>
@@ -14424,7 +14424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>18</v>
       </c>
@@ -14477,7 +14477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>18</v>
       </c>
@@ -14530,7 +14530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>18</v>
       </c>
@@ -14583,7 +14583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>18</v>
       </c>
@@ -14621,10 +14621,10 @@
         <v>49</v>
       </c>
       <c r="M133" s="4" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="N133" s="4" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="O133">
         <v>1.6479999999999999</v>
@@ -14636,7 +14636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>18</v>
       </c>
@@ -14689,7 +14689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>18</v>
       </c>
@@ -14742,7 +14742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>18</v>
       </c>
@@ -14795,7 +14795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>18</v>
       </c>
@@ -14848,7 +14848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>18</v>
       </c>
@@ -14901,7 +14901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>18</v>
       </c>
@@ -14954,7 +14954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>18</v>
       </c>
@@ -15007,7 +15007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>18</v>
       </c>
@@ -15060,7 +15060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>18</v>
       </c>
@@ -15113,7 +15113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>18</v>
       </c>
@@ -15166,7 +15166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>18</v>
       </c>
@@ -15219,7 +15219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>18</v>
       </c>
@@ -15272,7 +15272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>18</v>
       </c>
@@ -15325,7 +15325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>18</v>
       </c>
@@ -15378,7 +15378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>18</v>
       </c>
@@ -15431,7 +15431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>18</v>
       </c>
@@ -15484,7 +15484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>18</v>
       </c>
@@ -15537,7 +15537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>18</v>
       </c>
@@ -15590,7 +15590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>18</v>
       </c>
@@ -15643,7 +15643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>18</v>
       </c>
@@ -15696,7 +15696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>18</v>
       </c>
@@ -15749,7 +15749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>18</v>
       </c>
@@ -15802,7 +15802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>18</v>
       </c>
@@ -15855,7 +15855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>18</v>
       </c>
@@ -15908,7 +15908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>18</v>
       </c>
@@ -15961,7 +15961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>18</v>
       </c>
@@ -16014,7 +16014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>18</v>
       </c>
@@ -16067,7 +16067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>18</v>
       </c>
@@ -16120,7 +16120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>18</v>
       </c>
@@ -16173,7 +16173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>18</v>
       </c>
@@ -16226,7 +16226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>18</v>
       </c>
@@ -16279,7 +16279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>18</v>
       </c>
@@ -16332,7 +16332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>18</v>
       </c>
@@ -16385,7 +16385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>18</v>
       </c>
@@ -16438,7 +16438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>18</v>
       </c>
@@ -16491,7 +16491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>18</v>
       </c>
@@ -16544,7 +16544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>18</v>
       </c>
@@ -16597,7 +16597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>18</v>
       </c>
@@ -16650,7 +16650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>18</v>
       </c>
@@ -16703,7 +16703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>18</v>
       </c>
@@ -16756,7 +16756,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>18</v>
       </c>
@@ -16809,7 +16809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>18</v>
       </c>
@@ -16862,7 +16862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>18</v>
       </c>
@@ -16915,7 +16915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>18</v>
       </c>
@@ -16968,7 +16968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>18</v>
       </c>
@@ -17021,7 +17021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>18</v>
       </c>
@@ -17074,7 +17074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>18</v>
       </c>
@@ -17127,7 +17127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>18</v>
       </c>
@@ -17180,7 +17180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>18</v>
       </c>
@@ -17233,7 +17233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>18</v>
       </c>
@@ -17286,7 +17286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>18</v>
       </c>
@@ -17339,7 +17339,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>18</v>
       </c>
@@ -17392,7 +17392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>18</v>
       </c>
@@ -17445,7 +17445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>18</v>
       </c>
@@ -17498,7 +17498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>18</v>
       </c>
@@ -17551,7 +17551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>18</v>
       </c>
@@ -17604,7 +17604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>18</v>
       </c>
@@ -17657,7 +17657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>18</v>
       </c>
@@ -17710,7 +17710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>18</v>
       </c>
@@ -17763,7 +17763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>18</v>
       </c>
@@ -17816,7 +17816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>18</v>
       </c>
@@ -17869,7 +17869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>18</v>
       </c>
@@ -17922,7 +17922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>18</v>
       </c>
@@ -17975,7 +17975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>18</v>
       </c>
@@ -18028,7 +18028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>18</v>
       </c>
@@ -18081,7 +18081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>18</v>
       </c>
@@ -18134,7 +18134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>18</v>
       </c>
@@ -18187,7 +18187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>18</v>
       </c>
@@ -18240,7 +18240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>18</v>
       </c>
@@ -18293,7 +18293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>18</v>
       </c>
@@ -18346,7 +18346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>18</v>
       </c>
@@ -18399,7 +18399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>18</v>
       </c>
@@ -18452,7 +18452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>18</v>
       </c>
@@ -18505,7 +18505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>18</v>
       </c>
@@ -18558,7 +18558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>18</v>
       </c>
@@ -18611,7 +18611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>18</v>
       </c>
@@ -18664,7 +18664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>18</v>
       </c>
@@ -18717,7 +18717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>18</v>
       </c>
@@ -18770,7 +18770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>18</v>
       </c>
@@ -18823,7 +18823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>18</v>
       </c>
@@ -18876,7 +18876,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>18</v>
       </c>
@@ -18929,7 +18929,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>18</v>
       </c>
@@ -18982,7 +18982,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="216" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>18</v>
       </c>
@@ -19035,7 +19035,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>18</v>
       </c>
@@ -19088,7 +19088,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="218" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>18</v>
       </c>
@@ -19141,7 +19141,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="219" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>18</v>
       </c>
@@ -19194,7 +19194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>18</v>
       </c>
@@ -19247,7 +19247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>18</v>
       </c>
@@ -19300,7 +19300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>18</v>
       </c>
@@ -19353,7 +19353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>18</v>
       </c>
@@ -19406,7 +19406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>18</v>
       </c>
@@ -19459,7 +19459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>18</v>
       </c>
@@ -19512,7 +19512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>18</v>
       </c>
@@ -19565,7 +19565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>18</v>
       </c>
@@ -19618,7 +19618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>18</v>
       </c>
@@ -19671,7 +19671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>18</v>
       </c>
@@ -19724,7 +19724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>18</v>
       </c>
@@ -19777,7 +19777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>18</v>
       </c>
@@ -19830,7 +19830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>18</v>
       </c>
@@ -19883,7 +19883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>18</v>
       </c>
@@ -19936,7 +19936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>18</v>
       </c>
@@ -19989,7 +19989,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>18</v>
       </c>
@@ -20042,7 +20042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>18</v>
       </c>
@@ -20095,7 +20095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>18</v>
       </c>
@@ -20148,7 +20148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>18</v>
       </c>
@@ -20201,7 +20201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>18</v>
       </c>
@@ -20254,7 +20254,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="240" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>18</v>
       </c>
@@ -20307,7 +20307,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="241" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>18</v>
       </c>
@@ -20360,7 +20360,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="242" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>18</v>
       </c>
@@ -20413,7 +20413,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="243" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>18</v>
       </c>
@@ -20466,7 +20466,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="244" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>18</v>
       </c>
@@ -20519,7 +20519,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="245" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>18</v>
       </c>
@@ -20572,7 +20572,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="246" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>18</v>
       </c>
@@ -20625,7 +20625,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="247" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>18</v>
       </c>
@@ -20678,7 +20678,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="248" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>18</v>
       </c>
@@ -20731,7 +20731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>18</v>
       </c>
@@ -20784,7 +20784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>18</v>
       </c>
@@ -20837,7 +20837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>18</v>
       </c>
@@ -20890,7 +20890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>18</v>
       </c>
@@ -20943,7 +20943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>18</v>
       </c>
@@ -20996,7 +20996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>18</v>
       </c>
@@ -21049,7 +21049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>18</v>
       </c>
@@ -21090,7 +21090,7 @@
         <v>27</v>
       </c>
       <c r="N255" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O255">
         <v>1.1120000000000001</v>
@@ -21102,7 +21102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>18</v>
       </c>
@@ -21155,7 +21155,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>18</v>
       </c>
@@ -21208,7 +21208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>18</v>
       </c>
@@ -21261,7 +21261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>18</v>
       </c>
@@ -21314,7 +21314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>18</v>
       </c>
@@ -21367,7 +21367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>18</v>
       </c>
@@ -21420,7 +21420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>18</v>
       </c>
@@ -21473,7 +21473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>18</v>
       </c>
@@ -21526,7 +21526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>18</v>
       </c>
@@ -21579,7 +21579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>18</v>
       </c>
@@ -21632,7 +21632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>18</v>
       </c>
@@ -21685,7 +21685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>18</v>
       </c>
@@ -21738,7 +21738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>18</v>
       </c>
@@ -21791,7 +21791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>18</v>
       </c>
@@ -21844,7 +21844,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="270" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>18</v>
       </c>
@@ -21897,7 +21897,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="271" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>18</v>
       </c>
@@ -21950,7 +21950,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="272" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>18</v>
       </c>
@@ -22003,7 +22003,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="273" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>18</v>
       </c>
@@ -22056,7 +22056,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="274" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>18</v>
       </c>
@@ -22109,7 +22109,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="275" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>18</v>
       </c>
@@ -22162,7 +22162,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="276" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>18</v>
       </c>
@@ -22215,7 +22215,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="277" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>18</v>
       </c>
@@ -22268,7 +22268,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="278" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>18</v>
       </c>
@@ -22321,7 +22321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>18</v>
       </c>
@@ -22374,7 +22374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>18</v>
       </c>
@@ -22427,7 +22427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>18</v>
       </c>
@@ -22480,7 +22480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>18</v>
       </c>
@@ -22533,7 +22533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="283" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>18</v>
       </c>
@@ -22586,7 +22586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="284" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>18</v>
       </c>
@@ -22639,7 +22639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>18</v>
       </c>
@@ -22692,7 +22692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>18</v>
       </c>
@@ -22745,7 +22745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>18</v>
       </c>
@@ -22798,7 +22798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>18</v>
       </c>
@@ -22851,7 +22851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>18</v>
       </c>
@@ -22904,7 +22904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="290" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>18</v>
       </c>
@@ -22957,7 +22957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>18</v>
       </c>
@@ -23010,7 +23010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="292" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>18</v>
       </c>
@@ -23063,7 +23063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>18</v>
       </c>
@@ -23116,7 +23116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>18</v>
       </c>
@@ -23169,7 +23169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>18</v>
       </c>
@@ -23222,7 +23222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>18</v>
       </c>
@@ -23275,7 +23275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="297" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>18</v>
       </c>
@@ -23328,7 +23328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="298" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>18</v>
       </c>
@@ -23381,7 +23381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="299" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>18</v>
       </c>
@@ -23434,7 +23434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="300" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>18</v>
       </c>
@@ -23487,7 +23487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="301" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>18</v>
       </c>
@@ -23540,7 +23540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>18</v>
       </c>
@@ -23593,7 +23593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>18</v>
       </c>
@@ -23646,7 +23646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>18</v>
       </c>
@@ -23699,7 +23699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="305" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>18</v>
       </c>
@@ -23752,7 +23752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="306" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>18</v>
       </c>
@@ -23805,7 +23805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="307" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>18</v>
       </c>
@@ -23858,7 +23858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="308" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>18</v>
       </c>
@@ -23911,7 +23911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="309" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>18</v>
       </c>
@@ -23964,7 +23964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="310" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>18</v>
       </c>
@@ -24017,7 +24017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="311" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>18</v>
       </c>
@@ -24070,7 +24070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="312" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>18</v>
       </c>
@@ -24123,7 +24123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>18</v>
       </c>
@@ -24176,7 +24176,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="314" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>18</v>
       </c>
@@ -24229,7 +24229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="315" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>18</v>
       </c>
@@ -24282,7 +24282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="316" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>18</v>
       </c>
@@ -24335,7 +24335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="317" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>18</v>
       </c>
@@ -24388,7 +24388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="318" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>18</v>
       </c>
@@ -24441,7 +24441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="319" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>18</v>
       </c>
@@ -24494,7 +24494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>18</v>
       </c>
@@ -24547,7 +24547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A321" s="7" t="s">
         <v>18</v>
       </c>
@@ -24600,7 +24600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A322" s="7" t="s">
         <v>18</v>
       </c>
@@ -24653,7 +24653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A323" s="7" t="s">
         <v>18</v>
       </c>
@@ -24706,7 +24706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A324" s="7" t="s">
         <v>18</v>
       </c>
@@ -24759,7 +24759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A325" s="7" t="s">
         <v>18</v>
       </c>
@@ -24812,7 +24812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A326" s="7" t="s">
         <v>18</v>
       </c>
@@ -24865,7 +24865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A327" s="7" t="s">
         <v>18</v>
       </c>
@@ -24918,7 +24918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A328" s="7" t="s">
         <v>18</v>
       </c>
@@ -24971,7 +24971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A329" s="7" t="s">
         <v>18</v>
       </c>
@@ -25024,7 +25024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A330" s="7" t="s">
         <v>18</v>
       </c>
@@ -25077,7 +25077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A331" s="7" t="s">
         <v>18</v>
       </c>
@@ -25130,7 +25130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A332" s="7" t="s">
         <v>18</v>
       </c>
@@ -25183,7 +25183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A333" s="7" t="s">
         <v>18</v>
       </c>
@@ -25224,7 +25224,7 @@
         <v>27</v>
       </c>
       <c r="N333" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O333" s="7" t="s">
         <v>34</v>
@@ -25236,7 +25236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A334" s="7" t="s">
         <v>18</v>
       </c>
@@ -25277,7 +25277,7 @@
         <v>27</v>
       </c>
       <c r="N334" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O334" s="7" t="s">
         <v>34</v>

--- a/data/raw/GLNPO 2024 Spring/Erie/D100/ER 92 D100 Spring 2024 24GE03I93 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Erie/D100/ER 92 D100 Spring 2024 24GE03I93 Zoop.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Erie\D100\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D52B578-E684-4FF0-BFE6-C731209F9AE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1038871E-722C-412E-92DC-C508F21D4F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5A6E5FA3-7B75-4989-850D-07454B29D73D}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="6" r:id="rId2"/>
+    <pivotCache cacheId="24" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4165" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4165" uniqueCount="97">
   <si>
     <t>SAMPLENUM</t>
   </si>
@@ -243,9 +243,6 @@
   </si>
   <si>
     <t>CYC</t>
-  </si>
-  <si>
-    <t>CALIM</t>
   </si>
   <si>
     <t>Harpacticoida spp.</t>
@@ -6704,7 +6701,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F6441CF6-97DD-433D-854C-8E6F4EAECB29}" name="PivotTable3" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F6441CF6-97DD-433D-854C-8E6F4EAECB29}" name="PivotTable3" cacheId="24" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="T2:Y24" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="16">
     <pivotField showAll="0"/>
@@ -7176,6 +7173,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D166227-B8EA-4D18-B0B4-6BA6ABAE192C}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:Y334"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7250,7 +7248,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -7303,13 +7301,13 @@
         <v>1</v>
       </c>
       <c r="T2" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="U2" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="U2" s="5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -7362,25 +7360,25 @@
         <v>1</v>
       </c>
       <c r="T3" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="U3" t="s">
         <v>21</v>
       </c>
       <c r="V3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="W3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="X3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Y3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -7445,7 +7443,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -7510,7 +7508,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -7578,7 +7576,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -7631,7 +7629,7 @@
         <v>1</v>
       </c>
       <c r="T7" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="U7">
         <v>0</v>
@@ -7646,7 +7644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -7699,7 +7697,7 @@
         <v>1</v>
       </c>
       <c r="T8" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U8">
         <v>0</v>
@@ -7714,7 +7712,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -7779,7 +7777,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -7844,7 +7842,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -7912,7 +7910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -7965,7 +7963,7 @@
         <v>1</v>
       </c>
       <c r="T12" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="U12">
         <v>1</v>
@@ -7980,7 +7978,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -8045,7 +8043,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -8110,7 +8108,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -8178,7 +8176,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -8231,7 +8229,7 @@
         <v>1</v>
       </c>
       <c r="T16" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U16">
         <v>0</v>
@@ -8249,7 +8247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -8317,7 +8315,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -8388,7 +8386,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -8456,7 +8454,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -8509,7 +8507,7 @@
         <v>1</v>
       </c>
       <c r="T20" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U20">
         <v>0</v>
@@ -8645,7 +8643,7 @@
         <v>1</v>
       </c>
       <c r="T22" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="U22">
         <v>0</v>
@@ -8660,7 +8658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -8728,7 +8726,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -8781,7 +8779,7 @@
         <v>1</v>
       </c>
       <c r="T24" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="U24">
         <v>274</v>
@@ -8799,7 +8797,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -8852,7 +8850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:25" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -8905,16 +8903,16 @@
         <v>1</v>
       </c>
       <c r="T26" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="U26" s="11" t="s">
         <v>90</v>
-      </c>
-      <c r="U26" s="11" t="s">
-        <v>91</v>
       </c>
       <c r="V26" s="12">
         <v>0.995</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:25" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -8968,13 +8966,13 @@
       </c>
       <c r="T27" s="15"/>
       <c r="U27" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="V27" s="12">
         <v>1.0029999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:25" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -9027,16 +9025,16 @@
         <v>1</v>
       </c>
       <c r="T28" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="V28" s="12">
         <v>0.997</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:25" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -9090,13 +9088,13 @@
       </c>
       <c r="T29" s="15"/>
       <c r="U29" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="V29">
         <v>1.0009999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:25" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -9149,14 +9147,14 @@
         <v>1</v>
       </c>
       <c r="T30" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="U30" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="U30" s="16" t="s">
-        <v>94</v>
-      </c>
       <c r="V30" s="17"/>
     </row>
-    <row r="31" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:25" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -9209,14 +9207,14 @@
         <v>1</v>
       </c>
       <c r="T31" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="U31" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="U31" s="16" t="s">
-        <v>96</v>
-      </c>
       <c r="V31" s="17"/>
     </row>
-    <row r="32" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:25" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -9269,12 +9267,12 @@
         <v>1</v>
       </c>
       <c r="T32" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="U32" s="16"/>
       <c r="V32" s="17"/>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -9327,7 +9325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -9380,7 +9378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -9433,7 +9431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>18</v>
       </c>
@@ -9486,7 +9484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -9539,7 +9537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -9592,7 +9590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -9645,7 +9643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>18</v>
       </c>
@@ -9698,7 +9696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -9751,7 +9749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -9804,7 +9802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -9857,7 +9855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -9910,7 +9908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -9966,7 +9964,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -10072,7 +10070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -10128,7 +10126,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -10181,7 +10179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -10234,7 +10232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -10287,7 +10285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -10340,7 +10338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -10393,7 +10391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -10446,7 +10444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -10499,7 +10497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -10552,7 +10550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -10605,7 +10603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -10658,7 +10656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -10711,7 +10709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -10764,7 +10762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -10817,7 +10815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -10870,7 +10868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>18</v>
       </c>
@@ -10923,7 +10921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -10976,7 +10974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>18</v>
       </c>
@@ -11029,7 +11027,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>18</v>
       </c>
@@ -11082,7 +11080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>18</v>
       </c>
@@ -11135,7 +11133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>18</v>
       </c>
@@ -11188,7 +11186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>18</v>
       </c>
@@ -11241,7 +11239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -11294,7 +11292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -11347,7 +11345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -11400,7 +11398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -11453,7 +11451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>18</v>
       </c>
@@ -11506,7 +11504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -11559,7 +11557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>18</v>
       </c>
@@ -11612,7 +11610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>18</v>
       </c>
@@ -11665,7 +11663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>18</v>
       </c>
@@ -11718,7 +11716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>18</v>
       </c>
@@ -11771,7 +11769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>18</v>
       </c>
@@ -11824,7 +11822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>18</v>
       </c>
@@ -11877,7 +11875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>18</v>
       </c>
@@ -11930,7 +11928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>18</v>
       </c>
@@ -11983,7 +11981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>18</v>
       </c>
@@ -12089,7 +12087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>18</v>
       </c>
@@ -12142,7 +12140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>18</v>
       </c>
@@ -12195,7 +12193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>18</v>
       </c>
@@ -12248,7 +12246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>18</v>
       </c>
@@ -12301,7 +12299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>18</v>
       </c>
@@ -12354,7 +12352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>18</v>
       </c>
@@ -12407,7 +12405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>18</v>
       </c>
@@ -12460,7 +12458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>18</v>
       </c>
@@ -12513,7 +12511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>18</v>
       </c>
@@ -12619,7 +12617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>18</v>
       </c>
@@ -12672,7 +12670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>18</v>
       </c>
@@ -12725,7 +12723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>18</v>
       </c>
@@ -12778,7 +12776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -12884,7 +12882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>18</v>
       </c>
@@ -12937,7 +12935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>18</v>
       </c>
@@ -12990,7 +12988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>18</v>
       </c>
@@ -13043,7 +13041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>18</v>
       </c>
@@ -13096,7 +13094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>18</v>
       </c>
@@ -13149,7 +13147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>18</v>
       </c>
@@ -13202,7 +13200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>18</v>
       </c>
@@ -13255,7 +13253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>18</v>
       </c>
@@ -13308,7 +13306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>18</v>
       </c>
@@ -13361,7 +13359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>18</v>
       </c>
@@ -13414,7 +13412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>18</v>
       </c>
@@ -13467,7 +13465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>18</v>
       </c>
@@ -13520,7 +13518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>18</v>
       </c>
@@ -13573,7 +13571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>18</v>
       </c>
@@ -13626,7 +13624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>18</v>
       </c>
@@ -13679,7 +13677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>18</v>
       </c>
@@ -13732,7 +13730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>18</v>
       </c>
@@ -13785,7 +13783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>18</v>
       </c>
@@ -13838,7 +13836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>18</v>
       </c>
@@ -13894,7 +13892,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>18</v>
       </c>
@@ -13947,7 +13945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>18</v>
       </c>
@@ -14000,7 +13998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>18</v>
       </c>
@@ -14053,7 +14051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>18</v>
       </c>
@@ -14106,7 +14104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>18</v>
       </c>
@@ -14159,7 +14157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>18</v>
       </c>
@@ -14212,7 +14210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>18</v>
       </c>
@@ -14265,7 +14263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>18</v>
       </c>
@@ -14318,7 +14316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>18</v>
       </c>
@@ -14371,7 +14369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>18</v>
       </c>
@@ -14424,7 +14422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>18</v>
       </c>
@@ -14477,7 +14475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>18</v>
       </c>
@@ -14530,7 +14528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>18</v>
       </c>
@@ -14620,11 +14618,11 @@
       <c r="L133" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="M133" s="4" t="s">
-        <v>67</v>
+      <c r="M133" t="s">
+        <v>37</v>
       </c>
       <c r="N133" s="4" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="O133">
         <v>1.6479999999999999</v>
@@ -14636,7 +14634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>18</v>
       </c>
@@ -14689,7 +14687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>18</v>
       </c>
@@ -14742,7 +14740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>18</v>
       </c>
@@ -14795,7 +14793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>18</v>
       </c>
@@ -14848,7 +14846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>18</v>
       </c>
@@ -14901,7 +14899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>18</v>
       </c>
@@ -14954,7 +14952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>18</v>
       </c>
@@ -15007,7 +15005,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>18</v>
       </c>
@@ -15060,7 +15058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>18</v>
       </c>
@@ -15113,7 +15111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>18</v>
       </c>
@@ -15166,7 +15164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>18</v>
       </c>
@@ -15219,7 +15217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>18</v>
       </c>
@@ -15272,7 +15270,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>18</v>
       </c>
@@ -15325,7 +15323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>18</v>
       </c>
@@ -15378,7 +15376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>18</v>
       </c>
@@ -15431,7 +15429,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>18</v>
       </c>
@@ -15484,7 +15482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>18</v>
       </c>
@@ -15537,7 +15535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>18</v>
       </c>
@@ -15590,7 +15588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>18</v>
       </c>
@@ -15643,7 +15641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>18</v>
       </c>
@@ -15696,7 +15694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>18</v>
       </c>
@@ -15749,7 +15747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>18</v>
       </c>
@@ -15802,7 +15800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>18</v>
       </c>
@@ -15855,7 +15853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>18</v>
       </c>
@@ -15908,7 +15906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>18</v>
       </c>
@@ -15961,7 +15959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>18</v>
       </c>
@@ -16014,7 +16012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>18</v>
       </c>
@@ -16067,7 +16065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>18</v>
       </c>
@@ -16120,7 +16118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>18</v>
       </c>
@@ -16173,7 +16171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>18</v>
       </c>
@@ -16226,7 +16224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>18</v>
       </c>
@@ -16279,7 +16277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>18</v>
       </c>
@@ -16332,7 +16330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>18</v>
       </c>
@@ -16385,7 +16383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>18</v>
       </c>
@@ -16438,7 +16436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>18</v>
       </c>
@@ -16491,7 +16489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>18</v>
       </c>
@@ -16544,7 +16542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>18</v>
       </c>
@@ -16650,7 +16648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>18</v>
       </c>
@@ -16703,7 +16701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>18</v>
       </c>
@@ -16756,7 +16754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>18</v>
       </c>
@@ -16809,7 +16807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>18</v>
       </c>
@@ -16862,7 +16860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>18</v>
       </c>
@@ -16894,16 +16892,16 @@
         <v>24</v>
       </c>
       <c r="K176" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="L176" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="L176" s="3" t="s">
+      <c r="M176" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="M176" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="N176" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O176">
         <v>0.67800000000000005</v>
@@ -16915,7 +16913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>18</v>
       </c>
@@ -16968,7 +16966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>18</v>
       </c>
@@ -17021,7 +17019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>18</v>
       </c>
@@ -17074,7 +17072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>18</v>
       </c>
@@ -17127,7 +17125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>18</v>
       </c>
@@ -17180,7 +17178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>18</v>
       </c>
@@ -17233,7 +17231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>18</v>
       </c>
@@ -17286,7 +17284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>18</v>
       </c>
@@ -17339,7 +17337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>18</v>
       </c>
@@ -17392,7 +17390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>18</v>
       </c>
@@ -17445,7 +17443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>18</v>
       </c>
@@ -17498,7 +17496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>18</v>
       </c>
@@ -17551,7 +17549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>18</v>
       </c>
@@ -17604,7 +17602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>18</v>
       </c>
@@ -17657,7 +17655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>18</v>
       </c>
@@ -17710,7 +17708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>18</v>
       </c>
@@ -17763,7 +17761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>18</v>
       </c>
@@ -17816,7 +17814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>18</v>
       </c>
@@ -17869,7 +17867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>18</v>
       </c>
@@ -17922,7 +17920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>18</v>
       </c>
@@ -17975,7 +17973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>18</v>
       </c>
@@ -18028,7 +18026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>18</v>
       </c>
@@ -18081,7 +18079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>18</v>
       </c>
@@ -18134,7 +18132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>18</v>
       </c>
@@ -18187,7 +18185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>18</v>
       </c>
@@ -18240,7 +18238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>18</v>
       </c>
@@ -18293,7 +18291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>18</v>
       </c>
@@ -18346,7 +18344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>18</v>
       </c>
@@ -18399,7 +18397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>18</v>
       </c>
@@ -18452,7 +18450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>18</v>
       </c>
@@ -18505,7 +18503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>18</v>
       </c>
@@ -18558,7 +18556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>18</v>
       </c>
@@ -18611,7 +18609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>18</v>
       </c>
@@ -18664,7 +18662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>18</v>
       </c>
@@ -18717,7 +18715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>18</v>
       </c>
@@ -18770,7 +18768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>18</v>
       </c>
@@ -18823,7 +18821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>18</v>
       </c>
@@ -18876,7 +18874,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>18</v>
       </c>
@@ -18929,7 +18927,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>18</v>
       </c>
@@ -18982,7 +18980,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="216" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>18</v>
       </c>
@@ -19035,7 +19033,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>18</v>
       </c>
@@ -19088,7 +19086,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="218" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>18</v>
       </c>
@@ -19155,7 +19153,7 @@
         <v>-1</v>
       </c>
       <c r="E219" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F219">
         <v>16</v>
@@ -19194,7 +19192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>18</v>
       </c>
@@ -19208,7 +19206,7 @@
         <v>-1</v>
       </c>
       <c r="E220" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F220">
         <v>16</v>
@@ -19247,7 +19245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>18</v>
       </c>
@@ -19261,7 +19259,7 @@
         <v>-1</v>
       </c>
       <c r="E221" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F221">
         <v>16</v>
@@ -19300,7 +19298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>18</v>
       </c>
@@ -19314,7 +19312,7 @@
         <v>-1</v>
       </c>
       <c r="E222" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F222">
         <v>16</v>
@@ -19353,7 +19351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>18</v>
       </c>
@@ -19367,7 +19365,7 @@
         <v>-1</v>
       </c>
       <c r="E223" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F223">
         <v>16</v>
@@ -19406,7 +19404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>18</v>
       </c>
@@ -19420,7 +19418,7 @@
         <v>-1</v>
       </c>
       <c r="E224" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F224">
         <v>16</v>
@@ -19459,7 +19457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>18</v>
       </c>
@@ -19473,7 +19471,7 @@
         <v>-1</v>
       </c>
       <c r="E225" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F225">
         <v>16</v>
@@ -19512,7 +19510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>18</v>
       </c>
@@ -19526,7 +19524,7 @@
         <v>-1</v>
       </c>
       <c r="E226" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F226">
         <v>16</v>
@@ -19565,7 +19563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>18</v>
       </c>
@@ -19579,7 +19577,7 @@
         <v>-1</v>
       </c>
       <c r="E227" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F227">
         <v>16</v>
@@ -19597,10 +19595,10 @@
         <v>24</v>
       </c>
       <c r="K227" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="L227" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="L227" s="2" t="s">
-        <v>73</v>
       </c>
       <c r="M227" s="2" t="s">
         <v>66</v>
@@ -19618,7 +19616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>18</v>
       </c>
@@ -19632,7 +19630,7 @@
         <v>-1</v>
       </c>
       <c r="E228" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F228">
         <v>16</v>
@@ -19671,7 +19669,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>18</v>
       </c>
@@ -19685,7 +19683,7 @@
         <v>-1</v>
       </c>
       <c r="E229" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F229">
         <v>16</v>
@@ -19724,7 +19722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>18</v>
       </c>
@@ -19738,7 +19736,7 @@
         <v>-1</v>
       </c>
       <c r="E230" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F230">
         <v>16</v>
@@ -19756,10 +19754,10 @@
         <v>24</v>
       </c>
       <c r="K230" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="L230" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="L230" s="2" t="s">
-        <v>73</v>
       </c>
       <c r="M230" s="2" t="s">
         <v>66</v>
@@ -19777,7 +19775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>18</v>
       </c>
@@ -19791,7 +19789,7 @@
         <v>-1</v>
       </c>
       <c r="E231" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F231">
         <v>16</v>
@@ -19830,7 +19828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>18</v>
       </c>
@@ -19844,7 +19842,7 @@
         <v>-1</v>
       </c>
       <c r="E232" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F232">
         <v>16</v>
@@ -19862,16 +19860,16 @@
         <v>24</v>
       </c>
       <c r="K232" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="L232" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="L232" s="3" t="s">
+      <c r="M232" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="M232" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="N232" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O232">
         <v>0.71699999999999997</v>
@@ -19883,7 +19881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>18</v>
       </c>
@@ -19897,7 +19895,7 @@
         <v>-1</v>
       </c>
       <c r="E233" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F233">
         <v>16</v>
@@ -19936,7 +19934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>18</v>
       </c>
@@ -19950,7 +19948,7 @@
         <v>-1</v>
       </c>
       <c r="E234" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F234">
         <v>16</v>
@@ -19989,7 +19987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>18</v>
       </c>
@@ -20003,7 +20001,7 @@
         <v>-1</v>
       </c>
       <c r="E235" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F235">
         <v>16</v>
@@ -20042,7 +20040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>18</v>
       </c>
@@ -20056,7 +20054,7 @@
         <v>-1</v>
       </c>
       <c r="E236" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F236">
         <v>16</v>
@@ -20095,7 +20093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>18</v>
       </c>
@@ -20109,7 +20107,7 @@
         <v>-1</v>
       </c>
       <c r="E237" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F237">
         <v>16</v>
@@ -20148,7 +20146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>18</v>
       </c>
@@ -20162,7 +20160,7 @@
         <v>-1</v>
       </c>
       <c r="E238" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F238">
         <v>16</v>
@@ -20201,7 +20199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>18</v>
       </c>
@@ -20215,7 +20213,7 @@
         <v>-1</v>
       </c>
       <c r="E239" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F239">
         <v>16</v>
@@ -20254,7 +20252,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="240" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>18</v>
       </c>
@@ -20268,7 +20266,7 @@
         <v>-1</v>
       </c>
       <c r="E240" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F240">
         <v>16</v>
@@ -20307,7 +20305,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="241" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>18</v>
       </c>
@@ -20321,7 +20319,7 @@
         <v>-1</v>
       </c>
       <c r="E241" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F241">
         <v>16</v>
@@ -20360,7 +20358,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="242" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>18</v>
       </c>
@@ -20374,7 +20372,7 @@
         <v>-1</v>
       </c>
       <c r="E242" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F242">
         <v>16</v>
@@ -20413,7 +20411,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="243" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>18</v>
       </c>
@@ -20427,7 +20425,7 @@
         <v>-1</v>
       </c>
       <c r="E243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F243">
         <v>16</v>
@@ -20466,7 +20464,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="244" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>18</v>
       </c>
@@ -20480,7 +20478,7 @@
         <v>-1</v>
       </c>
       <c r="E244" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F244">
         <v>16</v>
@@ -20519,7 +20517,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="245" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>18</v>
       </c>
@@ -20533,7 +20531,7 @@
         <v>-1</v>
       </c>
       <c r="E245" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F245">
         <v>16</v>
@@ -20572,7 +20570,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="246" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>18</v>
       </c>
@@ -20586,7 +20584,7 @@
         <v>-1</v>
       </c>
       <c r="E246" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F246">
         <v>16</v>
@@ -20625,7 +20623,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="247" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>18</v>
       </c>
@@ -20639,7 +20637,7 @@
         <v>-1</v>
       </c>
       <c r="E247" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F247">
         <v>16</v>
@@ -20678,7 +20676,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="248" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>18</v>
       </c>
@@ -20692,7 +20690,7 @@
         <v>-1</v>
       </c>
       <c r="E248" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F248">
         <v>16</v>
@@ -20731,7 +20729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>18</v>
       </c>
@@ -20745,7 +20743,7 @@
         <v>-1</v>
       </c>
       <c r="E249" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F249">
         <v>16</v>
@@ -20784,7 +20782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>18</v>
       </c>
@@ -20798,7 +20796,7 @@
         <v>-1</v>
       </c>
       <c r="E250" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F250">
         <v>16</v>
@@ -20851,7 +20849,7 @@
         <v>-1</v>
       </c>
       <c r="E251" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F251">
         <v>16</v>
@@ -20890,7 +20888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>18</v>
       </c>
@@ -20904,7 +20902,7 @@
         <v>-1</v>
       </c>
       <c r="E252" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F252">
         <v>16</v>
@@ -20922,16 +20920,16 @@
         <v>24</v>
       </c>
       <c r="K252" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="L252" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="L252" s="3" t="s">
+      <c r="M252" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="M252" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="N252" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O252">
         <v>0.97</v>
@@ -20943,7 +20941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>18</v>
       </c>
@@ -20957,7 +20955,7 @@
         <v>-1</v>
       </c>
       <c r="E253" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F253">
         <v>16</v>
@@ -20996,7 +20994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>18</v>
       </c>
@@ -21010,7 +21008,7 @@
         <v>-1</v>
       </c>
       <c r="E254" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F254">
         <v>16</v>
@@ -21049,7 +21047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>18</v>
       </c>
@@ -21063,7 +21061,7 @@
         <v>-1</v>
       </c>
       <c r="E255" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F255">
         <v>16</v>
@@ -21081,10 +21079,10 @@
         <v>24</v>
       </c>
       <c r="K255" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="L255" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="L255" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="M255" s="4" t="s">
         <v>27</v>
@@ -21102,7 +21100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>18</v>
       </c>
@@ -21116,7 +21114,7 @@
         <v>-1</v>
       </c>
       <c r="E256" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F256">
         <v>16</v>
@@ -21134,13 +21132,13 @@
         <v>24</v>
       </c>
       <c r="K256" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="L256" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="L256" s="2" t="s">
+      <c r="M256" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="M256" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="N256" s="2" t="s">
         <v>44</v>
@@ -21155,7 +21153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>18</v>
       </c>
@@ -21169,7 +21167,7 @@
         <v>-1</v>
       </c>
       <c r="E257" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F257">
         <v>16</v>
@@ -21222,7 +21220,7 @@
         <v>-1</v>
       </c>
       <c r="E258" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F258">
         <v>16</v>
@@ -21275,7 +21273,7 @@
         <v>-1</v>
       </c>
       <c r="E259" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F259">
         <v>16</v>
@@ -21328,7 +21326,7 @@
         <v>-1</v>
       </c>
       <c r="E260" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F260">
         <v>16</v>
@@ -21367,7 +21365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>18</v>
       </c>
@@ -21381,7 +21379,7 @@
         <v>-1</v>
       </c>
       <c r="E261" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F261">
         <v>16</v>
@@ -21420,7 +21418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>18</v>
       </c>
@@ -21434,7 +21432,7 @@
         <v>-1</v>
       </c>
       <c r="E262" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F262">
         <v>16</v>
@@ -21473,7 +21471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>18</v>
       </c>
@@ -21487,7 +21485,7 @@
         <v>-1</v>
       </c>
       <c r="E263" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F263">
         <v>16</v>
@@ -21526,7 +21524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>18</v>
       </c>
@@ -21540,7 +21538,7 @@
         <v>-1</v>
       </c>
       <c r="E264" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F264">
         <v>16</v>
@@ -21593,7 +21591,7 @@
         <v>-1</v>
       </c>
       <c r="E265" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F265">
         <v>16</v>
@@ -21632,7 +21630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>18</v>
       </c>
@@ -21646,7 +21644,7 @@
         <v>-1</v>
       </c>
       <c r="E266" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F266">
         <v>16</v>
@@ -21685,7 +21683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>18</v>
       </c>
@@ -21699,7 +21697,7 @@
         <v>-1</v>
       </c>
       <c r="E267" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F267">
         <v>16</v>
@@ -21738,7 +21736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>18</v>
       </c>
@@ -21752,7 +21750,7 @@
         <v>-1</v>
       </c>
       <c r="E268" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F268">
         <v>16</v>
@@ -21791,7 +21789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>18</v>
       </c>
@@ -21805,7 +21803,7 @@
         <v>-1</v>
       </c>
       <c r="E269" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F269">
         <v>16</v>
@@ -21844,7 +21842,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="270" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>18</v>
       </c>
@@ -21858,7 +21856,7 @@
         <v>-1</v>
       </c>
       <c r="E270" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F270">
         <v>16</v>
@@ -21897,7 +21895,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="271" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>18</v>
       </c>
@@ -21911,7 +21909,7 @@
         <v>-1</v>
       </c>
       <c r="E271" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F271">
         <v>16</v>
@@ -21950,7 +21948,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="272" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>18</v>
       </c>
@@ -21964,7 +21962,7 @@
         <v>-1</v>
       </c>
       <c r="E272" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F272">
         <v>16</v>
@@ -22003,7 +22001,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="273" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>18</v>
       </c>
@@ -22017,7 +22015,7 @@
         <v>-1</v>
       </c>
       <c r="E273" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F273">
         <v>16</v>
@@ -22056,7 +22054,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="274" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>18</v>
       </c>
@@ -22070,7 +22068,7 @@
         <v>-1</v>
       </c>
       <c r="E274" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F274">
         <v>16</v>
@@ -22109,7 +22107,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="275" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>18</v>
       </c>
@@ -22123,7 +22121,7 @@
         <v>-1</v>
       </c>
       <c r="E275" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F275">
         <v>16</v>
@@ -22162,7 +22160,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="276" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>18</v>
       </c>
@@ -22176,7 +22174,7 @@
         <v>-1</v>
       </c>
       <c r="E276" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F276">
         <v>16</v>
@@ -22215,7 +22213,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="277" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>18</v>
       </c>
@@ -22229,7 +22227,7 @@
         <v>-1</v>
       </c>
       <c r="E277" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F277">
         <v>16</v>
@@ -22282,7 +22280,7 @@
         <v>-1</v>
       </c>
       <c r="E278" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F278">
         <v>8</v>
@@ -22321,7 +22319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>18</v>
       </c>
@@ -22335,7 +22333,7 @@
         <v>-1</v>
       </c>
       <c r="E279" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F279">
         <v>8</v>
@@ -22374,7 +22372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>18</v>
       </c>
@@ -22388,7 +22386,7 @@
         <v>-1</v>
       </c>
       <c r="E280" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F280">
         <v>8</v>
@@ -22406,13 +22404,13 @@
         <v>24</v>
       </c>
       <c r="K280" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L280" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="L280" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="M280" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N280" t="s">
         <v>44</v>
@@ -22427,7 +22425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>18</v>
       </c>
@@ -22441,7 +22439,7 @@
         <v>-1</v>
       </c>
       <c r="E281" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F281">
         <v>8</v>
@@ -22459,16 +22457,16 @@
         <v>24</v>
       </c>
       <c r="K281" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="L281" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="L281" s="3" t="s">
+      <c r="M281" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="M281" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="N281" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O281">
         <v>0.47699999999999998</v>
@@ -22480,7 +22478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>18</v>
       </c>
@@ -22494,7 +22492,7 @@
         <v>-1</v>
       </c>
       <c r="E282" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F282">
         <v>8</v>
@@ -22512,16 +22510,16 @@
         <v>24</v>
       </c>
       <c r="K282" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="L282" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="L282" s="3" t="s">
+      <c r="M282" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="M282" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="N282" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O282">
         <v>0.874</v>
@@ -22533,7 +22531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="283" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>18</v>
       </c>
@@ -22547,7 +22545,7 @@
         <v>-1</v>
       </c>
       <c r="E283" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F283">
         <v>8</v>
@@ -22586,7 +22584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="284" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>18</v>
       </c>
@@ -22600,7 +22598,7 @@
         <v>-1</v>
       </c>
       <c r="E284" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F284">
         <v>8</v>
@@ -22618,13 +22616,13 @@
         <v>24</v>
       </c>
       <c r="K284" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L284" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="L284" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="M284" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N284" s="2" t="s">
         <v>44</v>
@@ -22639,7 +22637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>18</v>
       </c>
@@ -22653,7 +22651,7 @@
         <v>-1</v>
       </c>
       <c r="E285" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F285">
         <v>8</v>
@@ -22692,7 +22690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>18</v>
       </c>
@@ -22706,7 +22704,7 @@
         <v>-1</v>
       </c>
       <c r="E286" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F286">
         <v>8</v>
@@ -22745,7 +22743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>18</v>
       </c>
@@ -22759,7 +22757,7 @@
         <v>-1</v>
       </c>
       <c r="E287" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F287">
         <v>8</v>
@@ -22798,7 +22796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>18</v>
       </c>
@@ -22812,7 +22810,7 @@
         <v>-1</v>
       </c>
       <c r="E288" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F288">
         <v>8</v>
@@ -22851,7 +22849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>18</v>
       </c>
@@ -22865,7 +22863,7 @@
         <v>-1</v>
       </c>
       <c r="E289" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F289">
         <v>8</v>
@@ -22904,7 +22902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="290" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>18</v>
       </c>
@@ -22918,7 +22916,7 @@
         <v>-1</v>
       </c>
       <c r="E290" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F290">
         <v>8</v>
@@ -22936,16 +22934,16 @@
         <v>24</v>
       </c>
       <c r="K290" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="L290" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="L290" s="3" t="s">
+      <c r="M290" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="M290" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="N290" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O290">
         <v>0.85499999999999998</v>
@@ -22957,7 +22955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>18</v>
       </c>
@@ -22971,7 +22969,7 @@
         <v>-1</v>
       </c>
       <c r="E291" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F291">
         <v>8</v>
@@ -23024,7 +23022,7 @@
         <v>-1</v>
       </c>
       <c r="E292" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F292">
         <v>8</v>
@@ -23063,7 +23061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>18</v>
       </c>
@@ -23077,7 +23075,7 @@
         <v>-1</v>
       </c>
       <c r="E293" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F293">
         <v>8</v>
@@ -23095,10 +23093,10 @@
         <v>24</v>
       </c>
       <c r="K293" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="L293" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="L293" s="2" t="s">
-        <v>73</v>
       </c>
       <c r="M293" s="2" t="s">
         <v>66</v>
@@ -23116,7 +23114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>18</v>
       </c>
@@ -23130,7 +23128,7 @@
         <v>-1</v>
       </c>
       <c r="E294" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F294">
         <v>8</v>
@@ -23148,16 +23146,16 @@
         <v>24</v>
       </c>
       <c r="K294" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="L294" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="L294" s="3" t="s">
+      <c r="M294" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="M294" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="N294" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O294">
         <v>0.751</v>
@@ -23169,7 +23167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>18</v>
       </c>
@@ -23183,7 +23181,7 @@
         <v>-1</v>
       </c>
       <c r="E295" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F295">
         <v>8</v>
@@ -23201,13 +23199,13 @@
         <v>24</v>
       </c>
       <c r="K295" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L295" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="L295" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="M295" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N295" s="2" t="s">
         <v>44</v>
@@ -23222,7 +23220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>18</v>
       </c>
@@ -23236,7 +23234,7 @@
         <v>-1</v>
       </c>
       <c r="E296" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F296">
         <v>8</v>
@@ -23275,7 +23273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="297" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>18</v>
       </c>
@@ -23289,7 +23287,7 @@
         <v>-1</v>
       </c>
       <c r="E297" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F297">
         <v>8</v>
@@ -23307,13 +23305,13 @@
         <v>24</v>
       </c>
       <c r="K297" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L297" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="L297" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="M297" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N297" s="2" t="s">
         <v>44</v>
@@ -23328,7 +23326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="298" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>18</v>
       </c>
@@ -23342,7 +23340,7 @@
         <v>-1</v>
       </c>
       <c r="E298" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F298">
         <v>8</v>
@@ -23381,7 +23379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="299" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>18</v>
       </c>
@@ -23395,7 +23393,7 @@
         <v>-1</v>
       </c>
       <c r="E299" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F299">
         <v>8</v>
@@ -23434,7 +23432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="300" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>18</v>
       </c>
@@ -23448,7 +23446,7 @@
         <v>-1</v>
       </c>
       <c r="E300" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F300">
         <v>8</v>
@@ -23487,7 +23485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="301" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>18</v>
       </c>
@@ -23501,7 +23499,7 @@
         <v>-1</v>
       </c>
       <c r="E301" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F301">
         <v>8</v>
@@ -23519,13 +23517,13 @@
         <v>24</v>
       </c>
       <c r="K301" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L301" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="L301" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="M301" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N301" s="2" t="s">
         <v>44</v>
@@ -23540,7 +23538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>18</v>
       </c>
@@ -23554,7 +23552,7 @@
         <v>-1</v>
       </c>
       <c r="E302" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F302">
         <v>8</v>
@@ -23593,7 +23591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>18</v>
       </c>
@@ -23607,7 +23605,7 @@
         <v>-1</v>
       </c>
       <c r="E303" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F303">
         <v>8</v>
@@ -23625,16 +23623,16 @@
         <v>24</v>
       </c>
       <c r="K303" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="L303" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="L303" s="3" t="s">
+      <c r="M303" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="M303" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="N303" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O303">
         <v>0.84199999999999997</v>
@@ -23660,7 +23658,7 @@
         <v>-1</v>
       </c>
       <c r="E304" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F304">
         <v>8</v>
@@ -23699,7 +23697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="305" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>18</v>
       </c>
@@ -23713,7 +23711,7 @@
         <v>-1</v>
       </c>
       <c r="E305" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F305">
         <v>8</v>
@@ -23731,16 +23729,16 @@
         <v>24</v>
       </c>
       <c r="K305" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="L305" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="L305" s="3" t="s">
+      <c r="M305" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="M305" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="N305" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O305">
         <v>0.55000000000000004</v>
@@ -23752,7 +23750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="306" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>18</v>
       </c>
@@ -23766,7 +23764,7 @@
         <v>-1</v>
       </c>
       <c r="E306" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F306">
         <v>8</v>
@@ -23805,7 +23803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="307" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>18</v>
       </c>
@@ -23819,7 +23817,7 @@
         <v>-1</v>
       </c>
       <c r="E307" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F307">
         <v>8</v>
@@ -23858,7 +23856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="308" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>18</v>
       </c>
@@ -23872,7 +23870,7 @@
         <v>-1</v>
       </c>
       <c r="E308" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F308">
         <v>8</v>
@@ -23911,7 +23909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="309" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>18</v>
       </c>
@@ -23925,7 +23923,7 @@
         <v>-1</v>
       </c>
       <c r="E309" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F309">
         <v>8</v>
@@ -23964,7 +23962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="310" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>18</v>
       </c>
@@ -23978,7 +23976,7 @@
         <v>-1</v>
       </c>
       <c r="E310" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F310">
         <v>8</v>
@@ -24017,7 +24015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="311" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>18</v>
       </c>
@@ -24031,7 +24029,7 @@
         <v>-1</v>
       </c>
       <c r="E311" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F311">
         <v>8</v>
@@ -24070,7 +24068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="312" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>18</v>
       </c>
@@ -24084,7 +24082,7 @@
         <v>-1</v>
       </c>
       <c r="E312" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F312">
         <v>8</v>
@@ -24123,7 +24121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>18</v>
       </c>
@@ -24137,7 +24135,7 @@
         <v>-1</v>
       </c>
       <c r="E313" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F313">
         <v>8</v>
@@ -24176,7 +24174,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="314" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>18</v>
       </c>
@@ -24190,7 +24188,7 @@
         <v>-1</v>
       </c>
       <c r="E314" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F314">
         <v>4</v>
@@ -24208,13 +24206,13 @@
         <v>24</v>
       </c>
       <c r="K314" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="L314" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="L314" s="2" t="s">
+      <c r="M314" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="M314" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="N314" s="2" t="s">
         <v>44</v>
@@ -24229,7 +24227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="315" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>18</v>
       </c>
@@ -24243,7 +24241,7 @@
         <v>-1</v>
       </c>
       <c r="E315" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F315">
         <v>4</v>
@@ -24282,7 +24280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="316" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>18</v>
       </c>
@@ -24296,7 +24294,7 @@
         <v>-1</v>
       </c>
       <c r="E316" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F316">
         <v>4</v>
@@ -24335,7 +24333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="317" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>18</v>
       </c>
@@ -24349,7 +24347,7 @@
         <v>-1</v>
       </c>
       <c r="E317" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F317">
         <v>4</v>
@@ -24388,7 +24386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="318" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>18</v>
       </c>
@@ -24402,7 +24400,7 @@
         <v>-1</v>
       </c>
       <c r="E318" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F318">
         <v>4</v>
@@ -24441,7 +24439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="319" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>18</v>
       </c>
@@ -24455,7 +24453,7 @@
         <v>-1</v>
       </c>
       <c r="E319" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F319">
         <v>4</v>
@@ -24494,7 +24492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>18</v>
       </c>
@@ -24508,7 +24506,7 @@
         <v>-1</v>
       </c>
       <c r="E320" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F320">
         <v>4</v>
@@ -24547,7 +24545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:17" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" s="7" t="s">
         <v>18</v>
       </c>
@@ -24579,13 +24577,13 @@
         <v>24</v>
       </c>
       <c r="K321" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="L321" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="L321" s="7" t="s">
+      <c r="M321" s="7" t="s">
         <v>77</v>
-      </c>
-      <c r="M321" s="7" t="s">
-        <v>78</v>
       </c>
       <c r="N321" s="7" t="s">
         <v>44</v>
@@ -24600,7 +24598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:17" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" s="7" t="s">
         <v>18</v>
       </c>
@@ -24614,7 +24612,7 @@
         <v>-1</v>
       </c>
       <c r="E322" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F322" s="7">
         <v>8</v>
@@ -24632,13 +24630,13 @@
         <v>24</v>
       </c>
       <c r="K322" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="L322" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="L322" s="7" t="s">
+      <c r="M322" s="7" t="s">
         <v>77</v>
-      </c>
-      <c r="M322" s="7" t="s">
-        <v>78</v>
       </c>
       <c r="N322" s="7" t="s">
         <v>44</v>
@@ -24653,7 +24651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:17" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" s="7" t="s">
         <v>18</v>
       </c>
@@ -24685,13 +24683,13 @@
         <v>24</v>
       </c>
       <c r="K323" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="L323" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="L323" s="7" t="s">
-        <v>81</v>
-      </c>
       <c r="M323" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N323" s="7" t="s">
         <v>44</v>
@@ -24706,7 +24704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:17" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" s="7" t="s">
         <v>18</v>
       </c>
@@ -24720,7 +24718,7 @@
         <v>-1</v>
       </c>
       <c r="E324" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F324" s="7">
         <v>16</v>
@@ -24738,13 +24736,13 @@
         <v>24</v>
       </c>
       <c r="K324" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="L324" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="L324" s="7" t="s">
-        <v>81</v>
-      </c>
       <c r="M324" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N324" s="7" t="s">
         <v>44</v>
@@ -24759,7 +24757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:17" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" s="7" t="s">
         <v>18</v>
       </c>
@@ -24773,7 +24771,7 @@
         <v>-1</v>
       </c>
       <c r="E325" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F325" s="7">
         <v>16</v>
@@ -24812,7 +24810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:17" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" s="7" t="s">
         <v>18</v>
       </c>
@@ -24826,7 +24824,7 @@
         <v>-1</v>
       </c>
       <c r="E326" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F326" s="7">
         <v>8</v>
@@ -24865,7 +24863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:17" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" s="7" t="s">
         <v>18</v>
       </c>
@@ -24879,7 +24877,7 @@
         <v>-1</v>
       </c>
       <c r="E327" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F327" s="7">
         <v>8</v>
@@ -24918,7 +24916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:17" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" s="7" t="s">
         <v>18</v>
       </c>
@@ -24950,13 +24948,13 @@
         <v>24</v>
       </c>
       <c r="K328" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="L328" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="L328" s="7" t="s">
+      <c r="M328" s="7" t="s">
         <v>84</v>
-      </c>
-      <c r="M328" s="7" t="s">
-        <v>85</v>
       </c>
       <c r="N328" s="7" t="s">
         <v>44</v>
@@ -24971,7 +24969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:17" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" s="7" t="s">
         <v>18</v>
       </c>
@@ -24985,7 +24983,7 @@
         <v>-1</v>
       </c>
       <c r="E329" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F329" s="7">
         <v>16</v>
@@ -25003,13 +25001,13 @@
         <v>24</v>
       </c>
       <c r="K329" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="L329" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="L329" s="7" t="s">
+      <c r="M329" s="7" t="s">
         <v>84</v>
-      </c>
-      <c r="M329" s="7" t="s">
-        <v>85</v>
       </c>
       <c r="N329" s="7" t="s">
         <v>44</v>
@@ -25024,7 +25022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:17" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" s="7" t="s">
         <v>18</v>
       </c>
@@ -25038,7 +25036,7 @@
         <v>-1</v>
       </c>
       <c r="E330" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F330" s="7">
         <v>8</v>
@@ -25056,13 +25054,13 @@
         <v>24</v>
       </c>
       <c r="K330" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="L330" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="L330" s="7" t="s">
+      <c r="M330" s="7" t="s">
         <v>84</v>
-      </c>
-      <c r="M330" s="7" t="s">
-        <v>85</v>
       </c>
       <c r="N330" s="7" t="s">
         <v>44</v>
@@ -25077,7 +25075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:17" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" s="7" t="s">
         <v>18</v>
       </c>
@@ -25091,7 +25089,7 @@
         <v>-1</v>
       </c>
       <c r="E331" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F331" s="7">
         <v>8</v>
@@ -25130,7 +25128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:17" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" s="7" t="s">
         <v>18</v>
       </c>
@@ -25162,10 +25160,10 @@
         <v>24</v>
       </c>
       <c r="K332" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="L332" s="7" t="s">
         <v>72</v>
-      </c>
-      <c r="L332" s="7" t="s">
-        <v>73</v>
       </c>
       <c r="M332" s="7" t="s">
         <v>66</v>
@@ -25183,7 +25181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:17" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" s="7" t="s">
         <v>18</v>
       </c>
@@ -25215,10 +25213,10 @@
         <v>24</v>
       </c>
       <c r="K333" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="L333" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="L333" s="9" t="s">
-        <v>75</v>
       </c>
       <c r="M333" s="10" t="s">
         <v>27</v>
@@ -25236,7 +25234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:17" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" s="7" t="s">
         <v>18</v>
       </c>
@@ -25250,7 +25248,7 @@
         <v>-1</v>
       </c>
       <c r="E334" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F334" s="7">
         <v>8</v>
@@ -25268,10 +25266,10 @@
         <v>24</v>
       </c>
       <c r="K334" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="L334" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="L334" s="9" t="s">
-        <v>75</v>
       </c>
       <c r="M334" s="10" t="s">
         <v>27</v>
@@ -25290,6 +25288,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:R334" xr:uid="{6D166227-B8EA-4D18-B0B4-6BA6ABAE192C}">
+    <filterColumn colId="10">
+      <filters>
+        <filter val="Limnocalanus copepodites"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="5">
     <mergeCell ref="T26:T27"/>
     <mergeCell ref="T28:T29"/>
